--- a/SeleniumDataDrivenWorkbook.xlsx
+++ b/SeleniumDataDrivenWorkbook.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="testdata" sheetId="1" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>Test cases</t>
   </si>
   <si>
-    <t>Misir Ali</t>
-  </si>
-  <si>
     <t>Humayun</t>
   </si>
   <si>
@@ -110,16 +107,35 @@
   </si>
   <si>
     <t>BANG1994</t>
+  </si>
+  <si>
+    <t>Himu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -142,8 +158,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -151,7 +191,31 @@
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="25">
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -546,20 +610,21 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
